--- a/Fase 2/Evidencias Grupales/PLANILLA DE EVALUACION AVANCE FASE 2.xlsx
+++ b/Fase 2/Evidencias Grupales/PLANILLA DE EVALUACION AVANCE FASE 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manan\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF7B75B8-059C-4871-9C5A-6661F303D8E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{94EDE88C-D044-4C74-B21F-0CFDAE418AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="67">
   <si>
     <t>PUNTOS</t>
   </si>
@@ -278,13 +278,16 @@
     <t>No generan evidencias dentro del repositorio  del proyecto del aporte de cada uno de los integrantes del equipo por lo que no se permite identificar la equidad en el trabajo y la participación de cada estudiante</t>
   </si>
   <si>
+    <t>Ignacio Huerta</t>
+  </si>
+  <si>
     <t>Gerald Astargo</t>
   </si>
   <si>
     <t>Diego Espejo</t>
   </si>
   <si>
-    <t>Ignacio Huerta</t>
+    <t>x</t>
   </si>
 </sst>
 </file>
@@ -1291,7 +1294,7 @@
       </c>
       <c r="C4" s="5">
         <f>EVALUACION2!$C$22</f>
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="G4" s="1"/>
     </row>
@@ -1304,7 +1307,7 @@
       </c>
       <c r="C5" s="5">
         <f>EVALUACION2!$C$22</f>
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="G5" s="1"/>
     </row>
@@ -1317,7 +1320,7 @@
       </c>
       <c r="C6" s="5">
         <f>EVALUACION2!$C$22</f>
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="G6" s="1"/>
     </row>
@@ -1377,7 +1380,6 @@
         <v>X</v>
       </c>
       <c r="E13" s="15">
-        <f>IF(D13="X",100*0.1,"")</f>
         <v>10</v>
       </c>
       <c r="F13" s="15" t="str">
@@ -1418,17 +1420,12 @@
         <f t="shared" si="0"/>
         <v>X</v>
       </c>
-      <c r="E14" s="15">
-        <f>IF(D14="X",100*0.1,"")</f>
-        <v>10</v>
-      </c>
-      <c r="F14" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G14" s="15" t="str">
-        <f>IF(F14="X",60*0.1,"")</f>
-        <v/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="G14" s="15">
+        <v>6</v>
       </c>
       <c r="H14" s="15" t="str">
         <f t="shared" si="2"/>
@@ -1460,22 +1457,14 @@
         <f t="shared" si="0"/>
         <v>X</v>
       </c>
-      <c r="E15" s="15">
-        <f>IF(D15="X",100*0.25,"")</f>
-        <v>25</v>
-      </c>
-      <c r="F15" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G15" s="15" t="str">
-        <f>IF(F15="X",60*0.25,"")</f>
-        <v/>
-      </c>
-      <c r="H15" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="G15" s="15">
+        <v>15</v>
+      </c>
+      <c r="H15" s="15"/>
       <c r="I15" s="15" t="str">
         <f>IF(H15="X",30*0.25,"")</f>
         <v/>
@@ -1498,21 +1487,16 @@
       <c r="C16" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="D16" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>X</v>
-      </c>
-      <c r="E16" s="15">
-        <f>IF(D16="X",100*0.05,"")</f>
-        <v>5</v>
-      </c>
-      <c r="F16" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G16" s="15" t="str">
+      <c r="D16" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="G16" s="15">
         <f>IF(F16="X",60*0.05,"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="H16" s="15" t="str">
         <f t="shared" si="2"/>
@@ -1545,7 +1529,6 @@
         <v>X</v>
       </c>
       <c r="E17" s="15">
-        <f>IF(D17="X",100*0.05,"")</f>
         <v>5</v>
       </c>
       <c r="F17" s="15" t="str">
@@ -1587,7 +1570,6 @@
         <v>X</v>
       </c>
       <c r="E18" s="15">
-        <f>IF(D18="X",100*0.2,"")</f>
         <v>20</v>
       </c>
       <c r="F18" s="15" t="str">
@@ -1629,7 +1611,6 @@
         <v>X</v>
       </c>
       <c r="E19" s="15">
-        <f>IF(D19="X",100*0.15,"")</f>
         <v>15</v>
       </c>
       <c r="F19" s="15" t="str">
@@ -1671,7 +1652,6 @@
         <v>X</v>
       </c>
       <c r="E20" s="15">
-        <f>IF(D20="X",100*0.1,"")</f>
         <v>10</v>
       </c>
       <c r="F20" s="15" t="str">
@@ -1706,17 +1686,17 @@
       </c>
       <c r="C21" s="31">
         <f>E21+G21+I21+K21</f>
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="D21" s="16"/>
       <c r="E21" s="16">
         <f>SUM(E13:E20)</f>
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F21" s="16"/>
       <c r="G21" s="16">
         <f>SUM(G13:G20)</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H21" s="16"/>
       <c r="I21" s="16">
@@ -1736,7 +1716,7 @@
       </c>
       <c r="C22" s="17">
         <f>VLOOKUP(C21,ESCALA_IEP!A2:B202,2,FALSE)</f>
-        <v>7</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
